--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M28B4_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M28B4_IN_Piura.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>0.76</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>24.43</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C12" s="29">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>37.96</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>36.69</v>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.15</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1913,11 +1913,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>283.4283</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>99.99</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1938,11 +1938,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>71.4046</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>25.19</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1963,11 +1963,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>212.0237</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>74.81</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2161,11 +2161,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>283.5434</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2284,6 +2284,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2744,6 +2745,7 @@
       <c r="F23" s="17" t="inlineStr"/>
       <c r="G23" s="17" t="inlineStr"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
@@ -2788,6 +2790,7 @@
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28" ht="120" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
@@ -3213,11 +3216,11 @@
       </c>
       <c r="B18" s="33">
         <f>SUM(B10:B17)</f>
-        <v/>
+        <v>484.3</v>
       </c>
       <c r="C18" s="23">
         <f>SUM(C10:C17)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
@@ -3227,19 +3230,19 @@
       <c r="E18" s="17" t="inlineStr"/>
       <c r="F18" s="17">
         <f>ROUND(AVERAGE(F10:F17),2)</f>
-        <v/>
+        <v>25.51</v>
       </c>
       <c r="G18" s="22">
         <f>ROUND(AVERAGE(G10:G17),4)</f>
-        <v/>
+        <v>0.6021</v>
       </c>
       <c r="H18" s="23">
         <f>ROUND(AVERAGE(H10:H17),2)</f>
-        <v/>
+        <v>66.1</v>
       </c>
       <c r="I18" s="23">
         <f>ROUND(AVERAGE(I10:I17),2)</f>
-        <v/>
+        <v>32.65</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1">
